--- a/output/2026-09-06_10_Slovenia_Zasavska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-06_10_Slovenia_Zasavska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Confermato: rappresentante Nederman in Slovenia, focus su saldatura/legno/metalworking. Fonte: sito aziendale + Bizi/Companywall.</t>
+          <t>Confermato: rappresentante Nederman in Slovenia, focus su saldatura/legno/metalworking. Fonte: sito aziendale + Bizi/Companywall. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Confermato: azienda dal 1992, rappresentante ufficiale Nederman e ULT AG. Fonte: sito aziendale, Bizi, LinkedIn, metalindustry.info.</t>
+          <t>Confermato: azienda dal 1992, rappresentante ufficiale Nederman e ULT AG. Fonte: sito aziendale, Bizi, LinkedIn, metalindustry.info. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Azienda familiare dal 2005, produzione carpenteria metallica + linea impianti di aspirazione. Contatti reperiti da Companywall/Bizi, non dalla ricerca grezza iniziale - verificare che siano quelli della divisione Systems.</t>
+          <t>Azienda familiare dal 2005, produzione carpenteria metallica + linea impianti di aspirazione. Contatti reperiti da Companywall/Bizi, non dalla ricerca grezza iniziale - verificare che siano quelli della divisione Systems. [DUPLICATO — vedi anche: 2026-09-06_08_Slovenia_Zasavska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Confermato: distributore O.M.A.R./SO.TEC per aspirazione fumi/gas/vapori da saldatura, molatura, acciaio e legno.</t>
+          <t>Confermato: distributore O.M.A.R./SO.TEC per aspirazione fumi/gas/vapori da saldatura, molatura, acciaio e legno. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Confermato distributore ufficiale GEOVENT (Danimarca). Indirizzo discordante tra fonti (P.P. 91 vs Mariborska cesta 86, Celje) - verificare quale sia corrente.</t>
+          <t>Confermato distributore ufficiale GEOVENT (Danimarca). Indirizzo discordante tra fonti (P.P. 91 vs Mariborska cesta 86, Celje) - verificare quale sia corrente. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Confermato: oltre 100 aspiratori industriali in catalogo, ma rivenditore generalista (aspirazione non è core business).</t>
+          <t>Confermato: oltre 100 aspiratori industriali in catalogo, ma rivenditore generalista (aspirazione non è core business). [DUPLICATO — vedi anche: 2026-09-06_01_Slovenia_Podravska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Confermato: catalogo include tavolo di aspirazione e dispositivo di aspirazione con filtro per polveri fini.</t>
+          <t>Confermato: catalogo include tavolo di aspirazione e dispositivo di aspirazione con filtro per polveri fini. [DUPLICATO — vedi anche: 2026-09-06_00_Slovenia_Podravska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Confermato: azienda dal 1991, catalogo B2B ampio. Aspiratore industriale multiuso ASA 25 L PC presente ma marginale nel catalogo generalista.</t>
+          <t>Confermato: azienda dal 1991, catalogo B2B ampio. Aspiratore industriale multiuso ASA 25 L PC presente ma marginale nel catalogo generalista. [DUPLICATO — vedi anche: 2026-09-06_04_Slovenia_Koroska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Confermato: rappresentante EWM e Telwin, pagine dedicate a sistemi di aspirazione fumi di saldatura. Stesso gruppo web di Ašer ma entità separata.</t>
+          <t>Confermato: rappresentante EWM e Telwin, pagine dedicate a sistemi di aspirazione fumi di saldatura. Stesso gruppo web di Ašer ma entità separata. [DUPLICATO — vedi anche: 2026-09-06_07_Slovenia_Savinjska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
